--- a/data/trans_orig/P36B16-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P36B16-Clase-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>9266</t>
+          <t>9268</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4648</t>
+          <t>4685</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17122</t>
+          <t>17592</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>6848</t>
+          <t>7551</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3554</t>
+          <t>3703</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12836</t>
+          <t>12933</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,22 +795,22 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>16114</t>
+          <t>16819</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9544</t>
+          <t>10332</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>24911</t>
+          <t>26710</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,57%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>48206</t>
+          <t>50164</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>36084</t>
+          <t>37360</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>63013</t>
+          <t>64212</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>64198</t>
+          <t>71607</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>52619</t>
+          <t>58968</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>78571</t>
+          <t>88810</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>18,22%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>112404</t>
+          <t>121771</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>94739</t>
+          <t>101325</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>131989</t>
+          <t>145285</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>13,99%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>307291</t>
+          <t>334683</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>284532</t>
+          <t>309792</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>329098</t>
+          <t>357841</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>60,82%</t>
+          <t>60,78%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>56,32%</t>
+          <t>56,26%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>65,14%</t>
+          <t>64,99%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>270357</t>
+          <t>288889</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>253214</t>
+          <t>270380</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>287851</t>
+          <t>307977</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>60,54%</t>
+          <t>59,26%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>56,7%</t>
+          <t>55,46%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>64,45%</t>
+          <t>63,17%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>577649</t>
+          <t>623572</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>549159</t>
+          <t>594658</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>605625</t>
+          <t>654233</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>60,69%</t>
+          <t>60,07%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>57,7%</t>
+          <t>57,28%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>63,63%</t>
+          <t>63,02%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>134249</t>
+          <t>149296</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>114390</t>
+          <t>129631</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>156225</t>
+          <t>171462</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>26,57%</t>
+          <t>27,11%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,64%</t>
+          <t>23,54%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>30,92%</t>
+          <t>31,14%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>103579</t>
+          <t>115569</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>89766</t>
+          <t>99859</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>118998</t>
+          <t>132142</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>23,71%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>20,48%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>26,64%</t>
+          <t>27,11%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>237829</t>
+          <t>264866</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>212678</t>
+          <t>239853</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>263920</t>
+          <t>291731</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>25,51%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>27,73%</t>
+          <t>28,1%</t>
         </is>
       </c>
     </row>
@@ -1177,32 +1177,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>6200</t>
+          <t>7207</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2515</t>
+          <t>3396</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>12563</t>
+          <t>13632</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1212,32 +1212,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1625</t>
+          <t>3897</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>638</t>
+          <t>1669</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>4130</t>
+          <t>8425</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>7824</t>
+          <t>11104</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4001</t>
+          <t>5963</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>13640</t>
+          <t>17919</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,73%</t>
         </is>
       </c>
     </row>
@@ -1290,17 +1290,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1325,17 +1325,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>446607</t>
+          <t>487513</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>446607</t>
+          <t>487513</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>446607</t>
+          <t>487513</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>951820</t>
+          <t>1038131</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>951820</t>
+          <t>1038131</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>951820</t>
+          <t>1038131</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1407,27 +1407,27 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>3384</t>
+          <t>3503</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1042</t>
+          <t>993</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8144</t>
+          <t>8697</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>5761</t>
+          <t>6419</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2481</t>
+          <t>2787</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12025</t>
+          <t>13092</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,17 +1477,17 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>9145</t>
+          <t>9921</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4925</t>
+          <t>5255</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>17073</t>
+          <t>18134</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,0%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>47595</t>
+          <t>50743</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>35547</t>
+          <t>37614</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>60940</t>
+          <t>64299</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>47280</t>
+          <t>52672</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>37324</t>
+          <t>42087</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>59912</t>
+          <t>64769</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>94875</t>
+          <t>103415</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>78974</t>
+          <t>88105</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>111891</t>
+          <t>123647</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,65%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>263807</t>
+          <t>276290</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>242839</t>
+          <t>254360</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>285711</t>
+          <t>299481</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>58,34%</t>
+          <t>57,18%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>53,7%</t>
+          <t>52,64%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>63,18%</t>
+          <t>61,98%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>218705</t>
+          <t>239417</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>201198</t>
+          <t>221905</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>235235</t>
+          <t>257776</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>57,3%</t>
+          <t>56,69%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>52,71%</t>
+          <t>52,55%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>61,63%</t>
+          <t>61,04%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>482511</t>
+          <t>515707</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>454466</t>
+          <t>487585</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>509515</t>
+          <t>548876</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>57,86%</t>
+          <t>56,95%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>54,5%</t>
+          <t>53,85%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>61,1%</t>
+          <t>60,62%</t>
         </is>
       </c>
     </row>
@@ -1746,32 +1746,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>126083</t>
+          <t>140644</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>108278</t>
+          <t>120592</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>147852</t>
+          <t>162410</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>27,88%</t>
+          <t>29,11%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,94%</t>
+          <t>24,96%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>32,7%</t>
+          <t>33,61%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1781,32 +1781,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>104613</t>
+          <t>116948</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>90745</t>
+          <t>101169</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>119757</t>
+          <t>133695</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>27,69%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>23,96%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,37%</t>
+          <t>31,66%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>230697</t>
+          <t>257592</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>205141</t>
+          <t>230426</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>255737</t>
+          <t>285428</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>27,66%</t>
+          <t>28,45%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>25,45%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>30,67%</t>
+          <t>31,52%</t>
         </is>
       </c>
     </row>
@@ -1859,32 +1859,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>11345</t>
+          <t>12033</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5631</t>
+          <t>6207</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>22137</t>
+          <t>23522</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1894,32 +1894,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>5346</t>
+          <t>6838</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2495</t>
+          <t>3455</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>10061</t>
+          <t>12309</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>16690</t>
+          <t>18871</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>10014</t>
+          <t>11673</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>27987</t>
+          <t>30519</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,37%</t>
         </is>
       </c>
     </row>
@@ -1972,17 +1972,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2007,17 +2007,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>381705</t>
+          <t>422294</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>381705</t>
+          <t>422294</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>381705</t>
+          <t>422294</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>833918</t>
+          <t>905506</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>833918</t>
+          <t>905506</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>833918</t>
+          <t>905506</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>2035</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7854</t>
+          <t>6328</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1315</t>
+          <t>1414</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -2134,12 +2134,12 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4901</t>
+          <t>4912</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>3350</t>
+          <t>3429</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>504</t>
+          <t>936</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8738</t>
+          <t>8594</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,31%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>31736</t>
+          <t>36719</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11426</t>
+          <t>27023</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>56694</t>
+          <t>51424</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>16297</t>
+          <t>17905</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>10983</t>
+          <t>12055</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>23272</t>
+          <t>26373</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>48033</t>
+          <t>54624</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>19914</t>
+          <t>41494</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>74526</t>
+          <t>69398</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>10,54%</t>
         </is>
       </c>
     </row>
@@ -2315,32 +2315,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>260039</t>
+          <t>282974</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>104954</t>
+          <t>258751</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>419891</t>
+          <t>305118</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>38,91%</t>
+          <t>60,0%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>54,87%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>62,83%</t>
+          <t>64,7%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2350,32 +2350,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>97765</t>
+          <t>106729</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>87597</t>
+          <t>95516</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>107578</t>
+          <t>116825</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>58,77%</t>
+          <t>57,1%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>52,66%</t>
+          <t>51,1%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>64,67%</t>
+          <t>62,5%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>357804</t>
+          <t>389702</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>166762</t>
+          <t>363483</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>513556</t>
+          <t>416795</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>42,87%</t>
+          <t>59,18%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>55,2%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>61,53%</t>
+          <t>63,29%</t>
         </is>
       </c>
     </row>
@@ -2428,32 +2428,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>114783</t>
+          <t>133055</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>44126</t>
+          <t>113780</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>191618</t>
+          <t>154036</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>28,21%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>24,13%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>28,67%</t>
+          <t>32,66%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2463,32 +2463,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>47375</t>
+          <t>56425</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>38439</t>
+          <t>45928</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>56904</t>
+          <t>65964</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>28,48%</t>
+          <t>30,19%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>24,57%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>34,21%</t>
+          <t>35,29%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>162158</t>
+          <t>189479</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>73948</t>
+          <t>167025</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>234820</t>
+          <t>212442</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>28,77%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>25,36%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>28,14%</t>
+          <t>32,26%</t>
         </is>
       </c>
     </row>
@@ -2541,32 +2541,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>259671</t>
+          <t>16850</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>19547</t>
+          <t>9723</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>504527</t>
+          <t>30566</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>38,86%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>75,5%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2576,32 +2576,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>3592</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1632</t>
+          <t>1990</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>7681</t>
+          <t>9543</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>263263</t>
+          <t>21306</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>22877</t>
+          <t>13364</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>566144</t>
+          <t>36998</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>31,54%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>67,83%</t>
+          <t>5,62%</t>
         </is>
       </c>
     </row>
@@ -2654,17 +2654,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2689,17 +2689,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>166345</t>
+          <t>186929</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>166345</t>
+          <t>186929</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>166345</t>
+          <t>186929</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>834609</t>
+          <t>658540</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>834609</t>
+          <t>658540</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>834609</t>
+          <t>658540</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>6451</t>
+          <t>11158</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2934</t>
+          <t>5499</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>13438</t>
+          <t>22911</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>6762</t>
+          <t>7513</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2505</t>
+          <t>3909</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>13507</t>
+          <t>13445</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>13213</t>
+          <t>18670</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>7716</t>
+          <t>11220</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>21798</t>
+          <t>29119</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,46%</t>
         </is>
       </c>
     </row>
@@ -2884,32 +2884,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>74416</t>
+          <t>84101</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>59113</t>
+          <t>66377</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>93600</t>
+          <t>106233</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2919,32 +2919,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>57216</t>
+          <t>62056</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>27284</t>
+          <t>50876</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>77795</t>
+          <t>75157</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2954,32 +2954,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>131632</t>
+          <t>146157</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>96759</t>
+          <t>123832</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>159093</t>
+          <t>172586</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>8,66%</t>
         </is>
       </c>
     </row>
@@ -2997,32 +2997,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>616389</t>
+          <t>662944</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>576854</t>
+          <t>622282</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>650863</t>
+          <t>695606</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>59,56%</t>
+          <t>58,57%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>55,74%</t>
+          <t>54,98%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>62,9%</t>
+          <t>61,46%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3032,32 +3032,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>477490</t>
+          <t>519288</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>250804</t>
+          <t>494559</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>613540</t>
+          <t>542738</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>48,88%</t>
+          <t>60,38%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>25,67%</t>
+          <t>57,51%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>62,81%</t>
+          <t>63,11%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3067,32 +3067,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1093879</t>
+          <t>1182232</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>775614</t>
+          <t>1141853</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1229836</t>
+          <t>1227734</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>54,38%</t>
+          <t>59,35%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>38,55%</t>
+          <t>57,33%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>61,13%</t>
+          <t>61,64%</t>
         </is>
       </c>
     </row>
@@ -3110,32 +3110,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>318817</t>
+          <t>351350</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>285668</t>
+          <t>319245</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>354886</t>
+          <t>386459</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>30,81%</t>
+          <t>31,04%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>27,61%</t>
+          <t>28,21%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>34,29%</t>
+          <t>34,14%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3145,32 +3145,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>420873</t>
+          <t>251587</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>265450</t>
+          <t>229113</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>688294</t>
+          <t>275508</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>43,08%</t>
+          <t>29,25%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>27,17%</t>
+          <t>26,64%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>70,46%</t>
+          <t>32,04%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>739690</t>
+          <t>602938</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>583494</t>
+          <t>563644</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1110495</t>
+          <t>642790</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>36,77%</t>
+          <t>30,27%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>29,0%</t>
+          <t>28,3%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>55,2%</t>
+          <t>32,27%</t>
         </is>
       </c>
     </row>
@@ -3223,32 +3223,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>18747</t>
+          <t>22290</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>11308</t>
+          <t>13881</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>28638</t>
+          <t>34110</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3258,32 +3258,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>14554</t>
+          <t>19547</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>6789</t>
+          <t>12110</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>24724</t>
+          <t>30084</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>33300</t>
+          <t>41837</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>21648</t>
+          <t>30269</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>47042</t>
+          <t>58427</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,93%</t>
         </is>
       </c>
     </row>
@@ -3336,17 +3336,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3371,17 +3371,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>976895</t>
+          <t>859991</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>976895</t>
+          <t>859991</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>976895</t>
+          <t>859991</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>2011714</t>
+          <t>1991834</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>2011714</t>
+          <t>1991834</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>2011714</t>
+          <t>1991834</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3453,32 +3453,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>3976</t>
+          <t>3846</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1240</t>
+          <t>1646</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>10377</t>
+          <t>10117</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3488,67 +3488,67 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>8964</t>
+          <t>11119</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>5019</t>
+          <t>6897</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>14731</t>
+          <t>17801</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
+          <t>1,34%</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>0,83%</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>2,15%</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>14965</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>9387</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>22456</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
           <t>1,07%</t>
         </is>
       </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>0,6%</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>1,75%</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>12939</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t>7314</t>
-        </is>
-      </c>
-      <c r="T28" s="2" t="inlineStr">
-        <is>
-          <t>19986</t>
-        </is>
-      </c>
-      <c r="U28" s="2" t="inlineStr">
-        <is>
-          <t>0,98%</t>
-        </is>
-      </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,61%</t>
         </is>
       </c>
     </row>
@@ -3566,32 +3566,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>33158</t>
+          <t>35573</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>24465</t>
+          <t>25203</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>47270</t>
+          <t>49364</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3601,32 +3601,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>63532</t>
+          <t>66357</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>46655</t>
+          <t>55736</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>82220</t>
+          <t>81458</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3636,32 +3636,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>96690</t>
+          <t>101930</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>76725</t>
+          <t>86554</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>118888</t>
+          <t>122501</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>8,77%</t>
         </is>
       </c>
     </row>
@@ -3679,32 +3679,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>270220</t>
+          <t>319491</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>247147</t>
+          <t>295200</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>291676</t>
+          <t>345451</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>56,88%</t>
+          <t>56,25%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>52,03%</t>
+          <t>51,98%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>61,4%</t>
+          <t>60,82%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3714,32 +3714,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>476177</t>
+          <t>491152</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>358438</t>
+          <t>466249</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>536296</t>
+          <t>514281</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>56,69%</t>
+          <t>59,22%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>42,68%</t>
+          <t>56,21%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>63,85%</t>
+          <t>62,01%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3749,32 +3749,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>746396</t>
+          <t>810644</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>617292</t>
+          <t>776686</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>804711</t>
+          <t>848259</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>56,76%</t>
+          <t>58,01%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>46,94%</t>
+          <t>55,58%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>61,2%</t>
+          <t>60,7%</t>
         </is>
       </c>
     </row>
@@ -3792,32 +3792,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>160132</t>
+          <t>196789</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>140321</t>
+          <t>174414</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>183144</t>
+          <t>222980</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>33,71%</t>
+          <t>34,65%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>29,54%</t>
+          <t>30,71%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>38,55%</t>
+          <t>39,26%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3827,32 +3827,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>281945</t>
+          <t>249649</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>219354</t>
+          <t>228550</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>415124</t>
+          <t>271851</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>33,57%</t>
+          <t>30,1%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>27,56%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>49,42%</t>
+          <t>32,78%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3862,32 +3862,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>442076</t>
+          <t>446438</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>381648</t>
+          <t>413053</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>588336</t>
+          <t>481312</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>33,62%</t>
+          <t>31,95%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>29,02%</t>
+          <t>29,56%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>44,74%</t>
+          <t>34,44%</t>
         </is>
       </c>
     </row>
@@ -3905,32 +3905,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>7561</t>
+          <t>12264</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>3372</t>
+          <t>6004</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>14594</t>
+          <t>24499</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3940,32 +3940,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>9303</t>
+          <t>11138</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>4931</t>
+          <t>6810</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>15854</t>
+          <t>17904</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3975,32 +3975,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>16864</t>
+          <t>23402</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>10698</t>
+          <t>15366</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>25499</t>
+          <t>35919</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,57%</t>
         </is>
       </c>
     </row>
@@ -4018,17 +4018,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4053,17 +4053,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>839921</t>
+          <t>829415</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>839921</t>
+          <t>829415</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>839921</t>
+          <t>829415</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,17 +4088,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>1314966</t>
+          <t>1397379</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>1314966</t>
+          <t>1397379</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>1314966</t>
+          <t>1397379</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4120,7 +4120,7 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -4135,7 +4135,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>2353</t>
+          <t>2695</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -4145,12 +4145,12 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>14810</t>
+          <t>14628</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -4160,7 +4160,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4170,32 +4170,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>5282</t>
+          <t>7066</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>2233</t>
+          <t>2920</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>11354</t>
+          <t>14254</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4205,32 +4205,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>7636</t>
+          <t>9761</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>3067</t>
+          <t>4748</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>16946</t>
+          <t>23460</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>2,17%</t>
         </is>
       </c>
     </row>
@@ -4248,32 +4248,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>17800</t>
+          <t>15842</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>6631</t>
+          <t>5852</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>37725</t>
+          <t>35806</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4283,32 +4283,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>99748</t>
+          <t>103281</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>81217</t>
+          <t>86691</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>120634</t>
+          <t>123474</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4318,32 +4318,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>117548</t>
+          <t>119123</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>96724</t>
+          <t>99230</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>145217</t>
+          <t>148105</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>13,7%</t>
         </is>
       </c>
     </row>
@@ -4361,32 +4361,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>149337</t>
+          <t>143543</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>121404</t>
+          <t>118589</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>173881</t>
+          <t>165006</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>62,09%</t>
+          <t>60,51%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>50,48%</t>
+          <t>49,99%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>72,3%</t>
+          <t>69,56%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4396,67 +4396,67 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>423799</t>
+          <t>459581</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>399631</t>
+          <t>430969</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>451927</t>
+          <t>487449</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>55,7%</t>
+          <t>54,47%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
+          <t>51,08%</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>57,77%</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t>733</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="inlineStr">
+        <is>
+          <t>603124</t>
+        </is>
+      </c>
+      <c r="S36" s="2" t="inlineStr">
+        <is>
+          <t>567790</t>
+        </is>
+      </c>
+      <c r="T36" s="2" t="inlineStr">
+        <is>
+          <t>641126</t>
+        </is>
+      </c>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>55,8%</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
           <t>52,53%</t>
         </is>
       </c>
-      <c r="P36" s="2" t="inlineStr">
-        <is>
-          <t>59,4%</t>
-        </is>
-      </c>
-      <c r="Q36" s="2" t="inlineStr">
-        <is>
-          <t>733</t>
-        </is>
-      </c>
-      <c r="R36" s="2" t="inlineStr">
-        <is>
-          <t>573136</t>
-        </is>
-      </c>
-      <c r="S36" s="2" t="inlineStr">
-        <is>
-          <t>539719</t>
-        </is>
-      </c>
-      <c r="T36" s="2" t="inlineStr">
-        <is>
-          <t>607688</t>
-        </is>
-      </c>
-      <c r="U36" s="2" t="inlineStr">
-        <is>
-          <t>57,24%</t>
-        </is>
-      </c>
-      <c r="V36" s="2" t="inlineStr">
-        <is>
-          <t>53,9%</t>
-        </is>
-      </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>60,69%</t>
+          <t>59,31%</t>
         </is>
       </c>
     </row>
@@ -4474,32 +4474,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>64103</t>
+          <t>67068</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>44162</t>
+          <t>44931</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>89623</t>
+          <t>89393</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>26,65%</t>
+          <t>28,27%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>18,94%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>37,26%</t>
+          <t>37,68%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4509,32 +4509,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>215981</t>
+          <t>256330</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>191819</t>
+          <t>227397</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>238608</t>
+          <t>284545</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>28,39%</t>
+          <t>30,38%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>25,21%</t>
+          <t>26,95%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>31,36%</t>
+          <t>33,73%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4544,32 +4544,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>280085</t>
+          <t>323398</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>249839</t>
+          <t>287319</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>311096</t>
+          <t>356886</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>27,97%</t>
+          <t>29,92%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>26,58%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>31,07%</t>
+          <t>33,02%</t>
         </is>
       </c>
     </row>
@@ -4587,32 +4587,32 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>6914</t>
+          <t>8080</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>2147</t>
+          <t>2230</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>19639</t>
+          <t>21892</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4622,22 +4622,22 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>15999</t>
+          <t>17450</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>9841</t>
+          <t>10919</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>25807</t>
+          <t>29408</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
@@ -4647,7 +4647,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4657,32 +4657,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>22913</t>
+          <t>25530</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>14377</t>
+          <t>16266</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>37368</t>
+          <t>43335</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>4,01%</t>
         </is>
       </c>
     </row>
@@ -4700,17 +4700,17 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4735,17 +4735,17 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>760809</t>
+          <t>843709</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>760809</t>
+          <t>843709</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>760809</t>
+          <t>843709</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4770,17 +4770,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>1001317</t>
+          <t>1080936</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>1001317</t>
+          <t>1080936</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>1001317</t>
+          <t>1080936</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4817,32 +4817,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>27465</t>
+          <t>32484</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>17102</t>
+          <t>20749</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>39355</t>
+          <t>47387</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4852,32 +4852,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>34932</t>
+          <t>41081</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>25735</t>
+          <t>31158</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>47136</t>
+          <t>54548</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4887,32 +4887,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>62397</t>
+          <t>73565</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>47403</t>
+          <t>57843</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>78165</t>
+          <t>91798</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,3%</t>
         </is>
       </c>
     </row>
@@ -4930,32 +4930,32 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>252911</t>
+          <t>273142</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>193486</t>
+          <t>238253</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>289916</t>
+          <t>311972</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4965,32 +4965,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>348271</t>
+          <t>373879</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>286028</t>
+          <t>343941</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>387717</t>
+          <t>409621</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5000,32 +5000,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>601182</t>
+          <t>647021</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>523283</t>
+          <t>598039</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>664641</t>
+          <t>696828</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,85%</t>
         </is>
       </c>
     </row>
@@ -5043,32 +5043,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>1867081</t>
+          <t>2019924</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>1494742</t>
+          <t>1955570</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>2030768</t>
+          <t>2081797</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>55,3%</t>
+          <t>58,68%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>44,27%</t>
+          <t>56,81%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>60,15%</t>
+          <t>60,47%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5078,32 +5078,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>1964294</t>
+          <t>2105056</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>1562348</t>
+          <t>2057838</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>2115720</t>
+          <t>2163556</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>54,99%</t>
+          <t>57,99%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>43,74%</t>
+          <t>56,69%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>59,23%</t>
+          <t>59,6%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5113,32 +5113,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>3831375</t>
+          <t>4124980</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>3195180</t>
+          <t>4041926</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>4085901</t>
+          <t>4208046</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>55,14%</t>
+          <t>58,33%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>45,98%</t>
+          <t>57,15%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>58,8%</t>
+          <t>59,5%</t>
         </is>
       </c>
     </row>
@@ -5156,32 +5156,32 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>918167</t>
+          <t>1038202</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>726194</t>
+          <t>971859</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>1009232</t>
+          <t>1092460</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>27,2%</t>
+          <t>30,16%</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>28,23%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>29,89%</t>
+          <t>31,73%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5191,32 +5191,32 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>1174367</t>
+          <t>1046509</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>996420</t>
+          <t>994138</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>1716644</t>
+          <t>1092673</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>32,87%</t>
+          <t>28,83%</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>27,89%</t>
+          <t>27,39%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>48,05%</t>
+          <t>30,1%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5226,32 +5226,32 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>2092534</t>
+          <t>2084711</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>1866552</t>
+          <t>2003663</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>2542629</t>
+          <t>2161517</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>30,12%</t>
+          <t>29,48%</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>26,86%</t>
+          <t>28,33%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>36,59%</t>
+          <t>30,56%</t>
         </is>
       </c>
     </row>
@@ -5269,32 +5269,32 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>310437</t>
+          <t>78724</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>65830</t>
+          <t>61073</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>872615</t>
+          <t>102043</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>25,85%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5304,32 +5304,32 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>50418</t>
+          <t>63326</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>37267</t>
+          <t>49760</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>65080</t>
+          <t>79294</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5339,32 +5339,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>360855</t>
+          <t>142049</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>112577</t>
+          <t>117930</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>1204541</t>
+          <t>172586</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>2,44%</t>
         </is>
       </c>
     </row>
@@ -5382,17 +5382,17 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5417,17 +5417,17 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>3572282</t>
+          <t>3629850</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>3572282</t>
+          <t>3629850</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>3572282</t>
+          <t>3629850</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5452,17 +5452,17 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>6948342</t>
+          <t>7072326</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>6948342</t>
+          <t>7072326</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>6948342</t>
+          <t>7072326</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
